--- a/server/src/openrater/rates/ingest/assets/nonprofit_do_gl.workbook.xlsx
+++ b/server/src/openrater/rates/ingest/assets/nonprofit_do_gl.workbook.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated from the self-contained synthetic D&amp;O + GL reference design embedded in generate_workbook.py.</t>
+          <t>Transcribed from docs/rating-algorithms/nonprofit_990_do_gl_rating_v1.xlsx (synthetic pre-filing D&amp;O + GL program for IRS-990 nonprofits).</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Authored unknown-value load</t>
+          <t>filed unknown-value load</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Authored unknown-value load</t>
+          <t>filed unknown-value load</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Authored unknown-value load</t>
+          <t>filed unknown-value load</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4114,7 +4114,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -4157,7 +4157,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -4200,7 +4200,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4243,7 +4243,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4286,7 +4286,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4360,7 +4360,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4403,7 +4403,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4446,7 +4446,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4489,7 +4489,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4532,7 +4532,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4575,7 +4575,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -5115,12 +5115,12 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Chains (round.nearest_dollar; per-coverage in reference cases — see gaps)</t>
+          <t>Chains (round.nearest_dollar; per-coverage in source — see gaps)</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>embedded-synthetic-reference</t>
+          <t>nonprofit_990_do_gl_rating_v1.xlsx</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Synthetic reference program (heuristic factors; no regulatory data). D&amp;O and GL rated as two towers; eligibility tier is a side verdict.</t>
+          <t>Synthetic pre-filing program (heuristic factors; no regulatory filing). D&amp;O and GL rated as two towers; eligibility tier is a side verdict.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The D&amp;O tower (unrounded; reference value rounds to $1 — tolerance 0.5).</t>
+          <t>The D&amp;O tower (unrounded; filed value rounds to $1 — tolerance 0.5).</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The GL tower (unrounded; reference value rounds to $1 — tolerance 0.5).</t>
+          <t>The GL tower (unrounded; filed value rounds to $1 — tolerance 0.5).</t>
         </is>
       </c>
     </row>
@@ -6814,12 +6814,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The synthetic design derives stress (total_expenses / total_revenue) and occupancy intensity (occupancy_expense / total_revenue) inside the plan; the workbook format has no derivation step (capability registry: formula_stage).</t>
+          <t>The source derives stress (total_expenses / total_revenue) and occupancy intensity (occupancy_expense / total_revenue) inside the plan; the workbook format has no derivation step (capability registry: formula_stage).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The synthetic design's Submit trigger includes 'payroll_band = Unknown' — a test for a missing field, which gates cannot express.</t>
+          <t>The source's Submit trigger includes 'payroll_band = Unknown' — a test for a missing field, which gates cannot express.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Unknown-payroll accounts rate with the authored 1.10 default factor and tier by the remaining rules.</t>
+          <t>Unknown-payroll accounts rate with the filed 1.10 default factor and tier by the remaining rules.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The subsection table notes '501(c) other — refer if unknown', but the synthetic design's Eligibility Tiers has no such rule. Transcribed as default_value=501c_other with the authored 1.10/1.05 factors and no submit rule.</t>
+          <t>The subsection table notes '501(c) other — refer if unknown', but the source's Eligibility Tiers has no such rule. Transcribed as default_value=501c_other with the filed 1.10/1.05 factors and no submit rule.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6910,22 +6910,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boundary-case decision: Lakeshore Arts occupancy is 2.08%, so the stated less-than-3% binning rule maps it to 01_under_03.</t>
+          <t>Source discrepancy: the 'Worked Examples' sheet bins Lakeshore Arts occupancy at 02_03_06 (GL 680) while 'Test Cases' bins 01_under_03 (GL 578). The stated binning rule (50000 / 2400000 = 2.08% &lt; 3%) supports Test Cases — transcribed accordingly.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Synthetic case np_004</t>
+          <t>Worked Examples vs Test Cases</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>np_004 expects GL 578 under the explicit binning rule.</t>
+          <t>np_004 expects GL 578 per the source's own Test Cases sheet.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The embedded expected cases round each coverage to $1 before summing; the platform's round is the plan-tail total-rounder (capability registry r2: per_coverage_rounding).</t>
+          <t>The source rounds each coverage to $1 before summing; the platform's round is the plan-tail total-rounder (capability registry r2: per_coverage_rounding).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Per-coverage expected premiums carry tolerance 0.5 (unrounded towers vs reference rounded values); the package total rounds once at the tail.</t>
+          <t>Per-coverage expected premiums carry tolerance 0.5 (unrounded towers vs filed rounded values); the package total rounds once at the tail.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Missing NTEE maps to the authored unknown level (1.50x both LOBs).</t>
+          <t>Missing NTEE maps to the filed unknown level (1.50x both LOBs).</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Binned into the 7 authored revenue bands.</t>
+          <t>Binned into the 7 filed revenue bands.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Absent -&gt; the authored unknown payroll load (table __default__ 1.10).</t>
+          <t>Absent -&gt; the filed unknown payroll load (table __default__ 1.10).</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7757,7 +7757,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -7829,7 +7829,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -7865,7 +7865,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7901,7 +7901,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7937,7 +7937,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7973,7 +7973,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -8009,7 +8009,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -8045,7 +8045,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -8081,7 +8081,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -8117,7 +8117,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -8153,7 +8153,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -8189,7 +8189,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -8225,7 +8225,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -8261,7 +8261,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -8297,7 +8297,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8333,7 +8333,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8369,7 +8369,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8405,7 +8405,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8441,7 +8441,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -8477,7 +8477,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -8513,7 +8513,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8549,7 +8549,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8585,7 +8585,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8621,7 +8621,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8657,7 +8657,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8693,7 +8693,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8733,7 +8733,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8773,7 +8773,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8813,7 +8813,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8853,7 +8853,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -8893,7 +8893,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8933,7 +8933,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8973,7 +8973,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11253,7 +11253,7 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11289,7 +11289,7 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11325,7 +11325,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11361,7 +11361,7 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11397,7 +11397,7 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11433,7 +11433,7 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11473,7 +11473,7 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11513,7 +11513,7 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11553,7 +11553,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11593,7 +11593,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11635,7 +11635,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,7 +11675,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11715,7 +11715,7 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11755,7 +11755,7 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11797,7 +11797,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -11837,7 +11837,7 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11877,7 +11877,7 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11917,7 +11917,7 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11957,7 +11957,7 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11999,7 +11999,7 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12539,7 +12539,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13739,7 +13739,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nonprofit D&amp;O + GL synthetic reference design v1</t>
+          <t>Nonprofit 990 D&amp;O+GL rating v1 (source workbook)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
